--- a/AAII_Financials/Quarterly/SANG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SANG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>SANG</t>
   </si>
@@ -1214,8 +1214,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>10</v>
+      <c r="D20" s="3">
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
@@ -1262,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="E21" s="3">
         <v>6200</v>
@@ -1778,8 +1778,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>10</v>
+      <c r="D32" s="3">
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
@@ -2104,7 +2104,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
         <v>100</v>
@@ -2245,7 +2245,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="E45" s="3">
         <v>4300</v>
